--- a/dataset_t6_grouped/results2/G5/G5_T8387_W0075F0001T0006Z000C1N5_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T8387_W0075F0001T0006Z000C1N5_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>14.02641521083388</v>
+        <v>2.279292471760505</v>
       </c>
       <c r="D2" t="n">
-        <v>19.60412798935435</v>
+        <v>3.185670798270082</v>
       </c>
       <c r="E2" t="n">
-        <v>1.500965176529438</v>
+        <v>0.2439068411860337</v>
       </c>
       <c r="F2" t="n">
-        <v>4.977942554083095</v>
+        <v>0.8089156650385031</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>17.67091695698851</v>
+        <v>2.871524005510633</v>
       </c>
       <c r="D3" t="n">
-        <v>27.73937841094929</v>
+        <v>4.507648991779259</v>
       </c>
       <c r="E3" t="n">
-        <v>1.500965176529438</v>
+        <v>0.2439068411860337</v>
       </c>
       <c r="F3" t="n">
-        <v>4.977942554083095</v>
+        <v>0.8089156650385031</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>15.4288573871217</v>
+        <v>2.507189325407277</v>
       </c>
       <c r="D4" t="n">
-        <v>15.80582161156451</v>
+        <v>2.568446011879234</v>
       </c>
       <c r="E4" t="n">
-        <v>1.500965176529438</v>
+        <v>0.2439068411860337</v>
       </c>
       <c r="F4" t="n">
-        <v>4.977942554083095</v>
+        <v>0.8089156650385031</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
